--- a/artfynd/A 52764-2024 artfynd.xlsx
+++ b/artfynd/A 52764-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1563386</v>
+        <v>78837834</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ströms naturskog, Vb</t>
+          <t>Ströms naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>757446.2544870756</v>
+        <v>757507</v>
       </c>
       <c r="R2" t="n">
-        <v>7074976.011426988</v>
+        <v>7074871</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-05-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-05-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,11 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1129765</v>
+        <v>101347454</v>
       </c>
       <c r="B3" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ströms naturskog, Vb</t>
+          <t>Ström NR, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>757446.2544870756</v>
+        <v>757424</v>
       </c>
       <c r="R3" t="n">
-        <v>7074976.011426988</v>
+        <v>7074621</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-05-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-05-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,11 +853,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -902,22 +862,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>78837834</v>
+        <v>132099335</v>
       </c>
       <c r="B4" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ströms naturreservat, Vb</t>
+          <t>Brännberget, Brännberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>757506.5630475758</v>
+        <v>757318</v>
       </c>
       <c r="R4" t="n">
-        <v>7074870.973486629</v>
+        <v>7074352</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-07-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-07-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,70 +954,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101347452</v>
+        <v>131714061</v>
       </c>
       <c r="B5" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ström NR, Vb</t>
+          <t>Mölle, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>757450.6503118337</v>
+        <v>757409</v>
       </c>
       <c r="R5" t="n">
-        <v>7074617.056183794</v>
+        <v>7074538</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,22 +1031,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,81 +1057,64 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>död gran</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Anna Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Anna Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131714059</v>
+        <v>1129765</v>
       </c>
       <c r="B6" t="n">
-        <v>57945</v>
+        <v>92632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mölle, Vb</t>
+          <t>Ströms naturskog, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>757450</v>
+        <v>757446</v>
       </c>
       <c r="R6" t="n">
-        <v>7074552</v>
+        <v>7074976</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,22 +1138,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2012-05-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2012-05-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,19 +1154,546 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>56778021</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ströms naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>757419</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7074597</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2016-01-31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2016-01-31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Torgny Nilsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>78837875</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ströms naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>757553</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7074820</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-07-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-07-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131714059</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mölle, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>757450</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7074552</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Anna Johansson</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Anna Johansson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>101347453</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ström NR, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>757434</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7074613</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>101347452</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ström NR, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>757451</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7074617</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>död gran</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52764-2024 artfynd.xlsx
+++ b/artfynd/A 52764-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78837834</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101347454</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132099335</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131714061</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1129765</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,6 +1299,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56778021</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1366,6 +1401,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78837875</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131714059</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1587,6 +1632,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101347453</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1694,8 +1744,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101347452</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>